--- a/bang_2.xlsx
+++ b/bang_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Viet\Desktop\tracuu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37A1033-2342-4746-9489-369543628EA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3738A219-C260-420F-8EFB-065908CABCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4EEDCE44-FD0D-44E3-AFF2-0E083E82AA8F}"/>
   </bookViews>
@@ -1656,13 +1656,13 @@
     <t>10A9</t>
   </si>
   <si>
-    <t>Văn-Địa-GD GD KT&amp;PL</t>
-  </si>
-  <si>
     <t>Địa-GD KT&amp;PL-Sinh-KTCN</t>
   </si>
   <si>
     <t>Địa-GD KT&amp;PL-Sinh-KTNN</t>
+  </si>
+  <si>
+    <t>Văn-Địa-GD KT&amp;PL</t>
   </si>
 </sst>
 </file>
@@ -2021,7 +2021,7 @@
     <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5703125" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3999,10 +3999,10 @@
         <v>536</v>
       </c>
       <c r="E99" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F99" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4019,10 +4019,10 @@
         <v>536</v>
       </c>
       <c r="E100" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F100" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4039,10 +4039,10 @@
         <v>536</v>
       </c>
       <c r="E101" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F101" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4059,10 +4059,10 @@
         <v>536</v>
       </c>
       <c r="E102" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F102" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -4079,10 +4079,10 @@
         <v>536</v>
       </c>
       <c r="E103" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F103" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -4099,10 +4099,10 @@
         <v>536</v>
       </c>
       <c r="E104" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F104" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4119,10 +4119,10 @@
         <v>536</v>
       </c>
       <c r="E105" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F105" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4139,10 +4139,10 @@
         <v>536</v>
       </c>
       <c r="E106" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F106" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4159,10 +4159,10 @@
         <v>536</v>
       </c>
       <c r="E107" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F107" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -4179,10 +4179,10 @@
         <v>536</v>
       </c>
       <c r="E108" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F108" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4199,10 +4199,10 @@
         <v>536</v>
       </c>
       <c r="E109" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F109" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -4219,10 +4219,10 @@
         <v>536</v>
       </c>
       <c r="E110" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F110" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -4239,10 +4239,10 @@
         <v>536</v>
       </c>
       <c r="E111" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F111" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4259,10 +4259,10 @@
         <v>536</v>
       </c>
       <c r="E112" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F112" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4279,10 +4279,10 @@
         <v>536</v>
       </c>
       <c r="E113" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F113" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4299,10 +4299,10 @@
         <v>536</v>
       </c>
       <c r="E114" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F114" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4319,10 +4319,10 @@
         <v>536</v>
       </c>
       <c r="E115" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F115" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4339,10 +4339,10 @@
         <v>536</v>
       </c>
       <c r="E116" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F116" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -4359,10 +4359,10 @@
         <v>536</v>
       </c>
       <c r="E117" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F117" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4379,10 +4379,10 @@
         <v>536</v>
       </c>
       <c r="E118" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F118" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4399,10 +4399,10 @@
         <v>536</v>
       </c>
       <c r="E119" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F119" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4419,10 +4419,10 @@
         <v>536</v>
       </c>
       <c r="E120" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F120" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4439,10 +4439,10 @@
         <v>536</v>
       </c>
       <c r="E121" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F121" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -4459,10 +4459,10 @@
         <v>536</v>
       </c>
       <c r="E122" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F122" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4479,10 +4479,10 @@
         <v>536</v>
       </c>
       <c r="E123" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F123" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4499,10 +4499,10 @@
         <v>536</v>
       </c>
       <c r="E124" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F124" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4519,10 +4519,10 @@
         <v>536</v>
       </c>
       <c r="E125" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F125" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4539,10 +4539,10 @@
         <v>536</v>
       </c>
       <c r="E126" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F126" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4559,10 +4559,10 @@
         <v>536</v>
       </c>
       <c r="E127" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F127" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4579,10 +4579,10 @@
         <v>536</v>
       </c>
       <c r="E128" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F128" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4599,10 +4599,10 @@
         <v>536</v>
       </c>
       <c r="E129" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F129" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4619,10 +4619,10 @@
         <v>536</v>
       </c>
       <c r="E130" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F130" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4639,10 +4639,10 @@
         <v>536</v>
       </c>
       <c r="E131" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F131" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4659,10 +4659,10 @@
         <v>536</v>
       </c>
       <c r="E132" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F132" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4679,10 +4679,10 @@
         <v>536</v>
       </c>
       <c r="E133" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F133" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4699,10 +4699,10 @@
         <v>536</v>
       </c>
       <c r="E134" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F134" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4719,10 +4719,10 @@
         <v>536</v>
       </c>
       <c r="E135" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F135" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4739,10 +4739,10 @@
         <v>536</v>
       </c>
       <c r="E136" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F136" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4759,10 +4759,10 @@
         <v>536</v>
       </c>
       <c r="E137" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F137" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4779,10 +4779,10 @@
         <v>537</v>
       </c>
       <c r="E138" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F138" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -4799,10 +4799,10 @@
         <v>537</v>
       </c>
       <c r="E139" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F139" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4819,10 +4819,10 @@
         <v>537</v>
       </c>
       <c r="E140" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F140" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4839,10 +4839,10 @@
         <v>537</v>
       </c>
       <c r="E141" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F141" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4859,10 +4859,10 @@
         <v>537</v>
       </c>
       <c r="E142" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F142" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4879,10 +4879,10 @@
         <v>537</v>
       </c>
       <c r="E143" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F143" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4899,10 +4899,10 @@
         <v>537</v>
       </c>
       <c r="E144" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F144" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,10 +4919,10 @@
         <v>537</v>
       </c>
       <c r="E145" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F145" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4939,10 +4939,10 @@
         <v>537</v>
       </c>
       <c r="E146" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F146" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4959,10 +4959,10 @@
         <v>537</v>
       </c>
       <c r="E147" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F147" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4979,10 +4979,10 @@
         <v>537</v>
       </c>
       <c r="E148" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F148" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4999,10 +4999,10 @@
         <v>537</v>
       </c>
       <c r="E149" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F149" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -5019,10 +5019,10 @@
         <v>537</v>
       </c>
       <c r="E150" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F150" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,10 +5039,10 @@
         <v>537</v>
       </c>
       <c r="E151" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F151" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -5059,10 +5059,10 @@
         <v>537</v>
       </c>
       <c r="E152" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F152" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -5079,10 +5079,10 @@
         <v>537</v>
       </c>
       <c r="E153" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F153" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -5099,10 +5099,10 @@
         <v>537</v>
       </c>
       <c r="E154" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F154" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5119,10 +5119,10 @@
         <v>537</v>
       </c>
       <c r="E155" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F155" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -5139,10 +5139,10 @@
         <v>537</v>
       </c>
       <c r="E156" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F156" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5159,10 +5159,10 @@
         <v>537</v>
       </c>
       <c r="E157" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F157" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5179,10 +5179,10 @@
         <v>537</v>
       </c>
       <c r="E158" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F158" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5199,10 +5199,10 @@
         <v>537</v>
       </c>
       <c r="E159" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F159" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5219,10 +5219,10 @@
         <v>537</v>
       </c>
       <c r="E160" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F160" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5239,10 +5239,10 @@
         <v>537</v>
       </c>
       <c r="E161" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F161" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5259,10 +5259,10 @@
         <v>537</v>
       </c>
       <c r="E162" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F162" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5279,10 +5279,10 @@
         <v>537</v>
       </c>
       <c r="E163" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F163" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5299,10 +5299,10 @@
         <v>537</v>
       </c>
       <c r="E164" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F164" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5319,10 +5319,10 @@
         <v>537</v>
       </c>
       <c r="E165" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F165" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5339,10 +5339,10 @@
         <v>537</v>
       </c>
       <c r="E166" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F166" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5359,10 +5359,10 @@
         <v>537</v>
       </c>
       <c r="E167" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F167" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -5379,10 +5379,10 @@
         <v>537</v>
       </c>
       <c r="E168" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F168" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5399,10 +5399,10 @@
         <v>537</v>
       </c>
       <c r="E169" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F169" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5419,10 +5419,10 @@
         <v>537</v>
       </c>
       <c r="E170" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F170" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5439,10 +5439,10 @@
         <v>537</v>
       </c>
       <c r="E171" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F171" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5459,10 +5459,10 @@
         <v>537</v>
       </c>
       <c r="E172" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F172" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5479,10 +5479,10 @@
         <v>537</v>
       </c>
       <c r="E173" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F173" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5499,10 +5499,10 @@
         <v>537</v>
       </c>
       <c r="E174" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F174" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -9279,10 +9279,10 @@
         <v>542</v>
       </c>
       <c r="E363" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F363" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -9299,10 +9299,10 @@
         <v>542</v>
       </c>
       <c r="E364" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F364" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -9319,10 +9319,10 @@
         <v>542</v>
       </c>
       <c r="E365" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F365" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -9339,10 +9339,10 @@
         <v>542</v>
       </c>
       <c r="E366" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F366" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -9359,10 +9359,10 @@
         <v>542</v>
       </c>
       <c r="E367" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F367" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -9379,10 +9379,10 @@
         <v>542</v>
       </c>
       <c r="E368" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F368" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -9399,10 +9399,10 @@
         <v>542</v>
       </c>
       <c r="E369" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F369" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -9419,10 +9419,10 @@
         <v>542</v>
       </c>
       <c r="E370" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F370" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -9439,10 +9439,10 @@
         <v>542</v>
       </c>
       <c r="E371" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F371" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -9459,10 +9459,10 @@
         <v>542</v>
       </c>
       <c r="E372" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F372" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -9479,10 +9479,10 @@
         <v>542</v>
       </c>
       <c r="E373" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F373" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -9499,10 +9499,10 @@
         <v>542</v>
       </c>
       <c r="E374" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F374" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -9519,10 +9519,10 @@
         <v>542</v>
       </c>
       <c r="E375" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F375" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -9539,10 +9539,10 @@
         <v>542</v>
       </c>
       <c r="E376" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F376" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -9559,10 +9559,10 @@
         <v>542</v>
       </c>
       <c r="E377" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F377" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -9579,10 +9579,10 @@
         <v>542</v>
       </c>
       <c r="E378" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F378" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -9599,10 +9599,10 @@
         <v>542</v>
       </c>
       <c r="E379" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F379" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -9619,10 +9619,10 @@
         <v>542</v>
       </c>
       <c r="E380" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F380" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -9639,10 +9639,10 @@
         <v>542</v>
       </c>
       <c r="E381" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F381" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -9659,10 +9659,10 @@
         <v>542</v>
       </c>
       <c r="E382" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F382" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -9679,10 +9679,10 @@
         <v>542</v>
       </c>
       <c r="E383" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F383" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -9699,10 +9699,10 @@
         <v>542</v>
       </c>
       <c r="E384" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F384" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -9719,10 +9719,10 @@
         <v>542</v>
       </c>
       <c r="E385" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F385" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -9739,10 +9739,10 @@
         <v>542</v>
       </c>
       <c r="E386" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F386" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -9759,10 +9759,10 @@
         <v>542</v>
       </c>
       <c r="E387" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F387" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -9779,10 +9779,10 @@
         <v>542</v>
       </c>
       <c r="E388" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F388" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -9799,10 +9799,10 @@
         <v>542</v>
       </c>
       <c r="E389" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F389" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -9819,10 +9819,10 @@
         <v>542</v>
       </c>
       <c r="E390" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F390" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -9839,10 +9839,10 @@
         <v>542</v>
       </c>
       <c r="E391" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F391" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -9859,10 +9859,10 @@
         <v>542</v>
       </c>
       <c r="E392" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F392" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -9879,10 +9879,10 @@
         <v>542</v>
       </c>
       <c r="E393" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F393" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -9899,10 +9899,10 @@
         <v>542</v>
       </c>
       <c r="E394" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F394" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -9919,10 +9919,10 @@
         <v>542</v>
       </c>
       <c r="E395" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F395" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -9939,10 +9939,10 @@
         <v>542</v>
       </c>
       <c r="E396" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F396" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -9959,10 +9959,10 @@
         <v>542</v>
       </c>
       <c r="E397" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F397" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -9979,10 +9979,10 @@
         <v>542</v>
       </c>
       <c r="E398" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F398" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
